--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -637,24 +637,24 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>65分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站德川路华夏东路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -756,24 +756,24 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站博兴路东陆路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -875,29 +875,29 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -994,29 +994,29 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1118,26 +1118,22 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 35分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1145,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1169,12 +1165,12 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1184,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1237,24 +1233,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
+          <t>07:20采样：该车到重点站唐陆公路锦绣东路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1264,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1293,7 +1289,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1313,12 +1309,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -1356,22 +1352,26 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>07:20采样：该车到重点站东陆路金海路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1423,13 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1437,24 +1441,24 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1467,34 +1471,34 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±10分钟</t>
+          <t>07:20采样：该车到重点站新德西路德翔路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1508,47 +1512,999 @@
       <c r="T9" s="2" t="inlineStr"/>
       <c r="U9" s="2" t="inlineStr">
         <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站新川路妙境路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站长岛路台儿庄路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W9" s="2" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X9" s="2" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>13/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
+      <c r="AA12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>7/8</t>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>12/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1123,17 +1123,21 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 35分钟</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1141,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1165,12 +1169,12 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1190,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1228,29 +1232,29 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站唐陆公路锦绣东路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±9分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1260,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1284,12 +1288,12 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1299,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1347,29 +1351,29 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站东陆路金海路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±15分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,12 +1407,12 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1418,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1466,29 +1470,29 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站新德西路德翔路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±13分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1498,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1522,12 +1526,12 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1537,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1585,29 +1589,29 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站新川路妙境路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1617,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,12 +1645,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1656,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1704,29 +1708,29 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站长岛路台儿庄路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1736,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1760,12 +1764,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1775,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1828,24 +1832,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±6分钟</t>
+          <t>08:22采样：该车到重点站唐陆公路川桥路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1855,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1884,7 +1888,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1904,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1951,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±10分钟</t>
+          <t>08:22采样：该车到重点站德川路华夏东路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数22分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1974,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2003,7 +2007,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2023,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2066,24 +2070,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±15分钟</t>
+          <t>08:22采样：该车到重点站唐陆公路龙东大道 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2117,12 +2121,12 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2142,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2185,24 +2189,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±13分钟</t>
+          <t>08:22采样：该车到重点站唐陆公路龙东大道 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2212,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2236,12 +2240,12 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2261,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2304,24 +2308,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±6分钟</t>
+          <t>08:11采样：该车到重点站东陆路新金桥路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2331,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2360,7 +2364,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2380,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2393,24 +2397,24 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2423,24 +2427,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±9分钟</t>
+          <t>08:22采样：该车到重点站德川路华夏东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2450,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2464,47 +2468,995 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>08:22采样：该车到重点站新川路华东路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>08:22采样：该车到重点站博兴路东陆路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>81.5</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>4/13</t>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1713,24 +1713,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1827,29 +1827,29 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站唐陆公路川桥路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1963,12 +1963,12 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站德川路华夏东路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数22分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2065,29 +2065,29 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站唐陆公路龙东大道 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2184,29 +2184,29 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站唐陆公路龙东大道 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±8分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2303,12 +2303,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2320,7 +2320,7 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站东陆路新金桥路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2422,29 +2422,29 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站德川路华夏东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2546,24 +2546,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站新川路华东路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±7分钟</t>
+          <t>09:21采样：该车到重点站平度路长岛路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数9分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2665,26 +2665,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站博兴路东陆路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:12采样，终点ETA 28分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2692,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,12 +2712,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2731,22 +2727,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2784,24 +2780,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±8分钟</t>
+          <t>09:21采样：该车到重点站佳林路金高路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2811,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2840,7 +2836,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2860,12 +2856,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2903,24 +2899,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±10分钟</t>
+          <t>09:21采样：该车到重点站唐陆公路创新路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数24分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2930,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,7 +2955,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2979,7 +2975,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3022,24 +3018,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±12分钟</t>
+          <t>09:21采样：该车到重点站唐陆公路锦绣东路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3049,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,12 +3069,12 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3098,12 +3094,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3218,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3256,19 +3252,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±12分钟</t>
+          <t>09:21采样：该车到重点站唐陆公路唐镇路 ETA 23分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3283,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3312,7 +3308,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3332,12 +3328,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3375,19 +3371,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±10分钟</t>
+          <t>09:21采样：该车到重点站长岛路台儿庄路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3402,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3431,32 +3427,746 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y25" s="2" t="inlineStr">
+      <c r="Y26" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z25" s="2" t="inlineStr">
+      <c r="Z26" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
+      <c r="AA26" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>93.5</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr">
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
         <is>
           <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,17 +2493,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2541,24 +2541,24 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站平度路长岛路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数9分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2660,27 +2660,31 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:12采样，终点ETA 28分钟</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2688,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,12 +2716,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2737,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2775,29 +2779,29 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站佳林路金高路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2807,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,12 +2835,12 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2846,22 +2850,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2898,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2911,12 +2915,12 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站唐陆公路创新路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数24分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2926,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2950,12 +2954,12 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2965,17 +2969,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3018,26 +3022,22 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站唐陆公路锦绣东路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:52采样，终点ETA 11分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3132,27 +3132,31 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -3160,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,17 +3188,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3204,17 +3208,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3247,29 +3251,29 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站唐陆公路唐镇路 ETA 23分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±12分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3279,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,12 +3307,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3318,17 +3322,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3366,29 +3370,29 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站长岛路台儿庄路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±10分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3398,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3422,12 +3426,12 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3437,22 +3441,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3490,26 +3494,22 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:22采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3604,29 +3604,29 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3728,24 +3728,24 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+          <t>10:22采样：该车到重点站德川路华夏东路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3794,22 +3794,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3847,24 +3847,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±8分钟</t>
+          <t>10:22采样：该车到重点站唐陆公路龙东大道 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3966,19 +3966,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+          <t>10:22采样：该车到重点站唐陆公路川桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4055,24 +4055,24 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4085,24 +4085,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±14分钟</t>
+          <t>10:22采样：该车到重点站博兴路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4126,47 +4126,999 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>10:22采样：该车到重点站新川路华东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>10:22采样：该车到重点站博兴路东陆路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="Y34" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>80.7</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>4/14</t>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>69分钟</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,22 +2850,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3489,27 +3489,31 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:22采样，终点ETA 13分钟</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3517,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,12 +3545,12 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3566,7 +3570,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3609,12 +3613,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -3636,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,22 +3679,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3723,29 +3727,29 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10:22采样：该车到重点站德川路华夏东路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±8分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3755,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3779,12 +3783,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3804,12 +3808,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3842,24 +3846,24 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>64分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10:22采样：该车到重点站唐陆公路龙东大道 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3874,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3898,12 +3902,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3913,22 +3917,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3961,29 +3965,29 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>67分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10:22采样：该车到重点站唐陆公路川桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3993,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4017,12 +4021,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4032,22 +4036,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4080,29 +4084,29 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10:22采样：该车到重点站博兴路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4112,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4136,12 +4140,12 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4161,12 +4165,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4199,29 +4203,29 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10:22采样：该车到重点站新川路华东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4231,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,12 +4259,12 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4270,22 +4274,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4318,24 +4322,24 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10:22采样：该车到重点站博兴路东陆路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -4350,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4374,12 +4378,12 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4399,7 +4403,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4442,26 +4446,22 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：11:22采样，终点ETA 25分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4508,22 +4508,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4556,29 +4556,29 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4627,17 +4627,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4685,19 +4685,19 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±9分钟</t>
+          <t>11:22采样：该车到重点站唐陆公路春雅路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4799,24 +4799,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±8分钟</t>
+          <t>11:22采样：该车到重点站东陆路金海路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4918,24 +4918,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±12分钟</t>
+          <t>11:22采样：该车到重点站新德西路德翔路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4994,12 +4994,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5007,24 +5007,24 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5037,34 +5037,34 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+          <t>11:22采样：该车到重点站长岛路台儿庄路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5078,47 +5078,761 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
+      <c r="AA40" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>79.3</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>5/14</t>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>67分钟</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数67分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>76.3</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>76.3</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,22 +3441,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,22 +3560,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,22 +3798,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,22 +4155,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,22 +4393,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4441,27 +4441,31 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:22采样，终点ETA 25分钟</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -4469,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4493,12 +4497,12 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4518,7 +4522,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4588,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4637,7 +4641,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4675,29 +4679,29 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11:22采样：该车到重点站唐陆公路春雅路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4707,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4731,12 +4735,12 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4756,12 +4760,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4798,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4804,14 +4808,14 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11:22采样：该车到重点站东陆路金海路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -4826,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4850,12 +4854,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4875,12 +4879,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4913,24 +4917,24 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11:22采样：该车到重点站新德西路德翔路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -4945,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4969,12 +4973,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4984,22 +4988,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5032,29 +5036,29 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11:22采样：该车到重点站长岛路台儿庄路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±13分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5064,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5088,12 +5092,12 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5113,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5151,29 +5155,29 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5183,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5207,12 +5211,12 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5222,22 +5226,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5275,24 +5279,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±11分钟</t>
+          <t>12:21采样：该车到重点站德川路华夏东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5302,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,12 +5330,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5351,12 +5355,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5394,26 +5398,22 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>67分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数67分钟估算，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 49分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5445,37 +5445,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5513,19 +5513,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
+          <t>12:21采样：该车到重点站唐陆公路川桥路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>12:21采样：该车到重点站新川路华东路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5751,24 +5751,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
+          <t>12:21采样：该车到重点站金杨路金桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,37 +5802,751 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X45" s="2" t="inlineStr">
+      <c r="X47" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y45" s="2" t="inlineStr">
+      <c r="Y47" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr">
-        <is>
-          <t>1/14</t>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>69分钟</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,17 +3322,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,22 +3560,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3922,17 +3922,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,17 +4512,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5274,29 +5274,29 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站德川路华夏东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数20分钟，约±6分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5393,27 +5393,31 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 49分钟</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5421,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5445,17 +5449,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5465,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5512,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5525,12 +5529,12 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站唐陆公路川桥路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5540,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5564,12 +5568,12 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5594,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5627,12 +5631,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5644,12 +5648,12 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站新川路华东路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5659,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,12 +5687,12 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5698,17 +5702,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5746,29 +5750,29 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站金杨路金桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5778,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,12 +5806,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5827,7 +5831,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5875,21 +5879,17 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:21采样，终点ETA 34分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5984,29 +5984,29 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6055,22 +6055,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6108,24 +6108,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+          <t>13:21采样：该车到重点站东陆路金海路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6227,24 +6227,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±8分钟</t>
+          <t>13:21采样：该车到重点站新川路妙境路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6417,17 +6417,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6546,7 +6546,483 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,22 +4155,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,22 +4393,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5869,27 +5869,31 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:21采样，终点ETA 34分钟</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5897,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,12 +5925,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5946,7 +5950,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5989,24 +5993,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6016,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6065,12 +6069,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6103,29 +6107,29 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站东陆路金海路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6135,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,12 +6163,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6184,12 +6188,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6226,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -6239,12 +6243,12 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站新川路妙境路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6254,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6278,12 +6282,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6293,22 +6297,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6346,24 +6350,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>60分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±8分钟</t>
+          <t>13:52采样：该车到重点站唐陆公路锦绣东路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6373,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6402,7 +6406,7 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6422,12 +6426,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -6465,24 +6469,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±6分钟</t>
+          <t>同车下一次反向发车15:00，减去该车自身同类时段历史终点停站中位数17分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6492,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6521,7 +6525,7 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6531,22 +6535,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6665,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6784,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6898,12 +6902,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7026,6 +7030,359 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,22 +3203,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,22 +5345,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6112,24 +6112,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6188,12 +6188,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6231,24 +6231,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6307,12 +6307,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6345,29 +6345,29 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>60分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>13:52采样：该车到重点站唐陆公路锦绣东路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6464,29 +6464,29 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车15:00，减去该车自身同类时段历史终点停站中位数17分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6520,12 +6520,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6600,14 +6600,10 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:22采样，终点ETA 39分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -6615,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6644,7 +6640,7 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6707,24 +6703,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±9分钟</t>
+          <t>14:22采样：该车到重点站唐陆公路龙东大道 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6734,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6763,7 +6759,7 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6773,22 +6769,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6826,24 +6822,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±7分钟</t>
+          <t>14:22采样：该车到重点站博兴路东陆路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6853,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6882,7 +6878,7 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6902,12 +6898,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6941,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -6957,12 +6953,12 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+          <t>14:22采样：该车到重点站唐陆公路龙东大道 ETA 32分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6972,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7001,7 +6997,7 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7091,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7140,12 +7136,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7268,24 +7264,24 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7298,34 +7294,34 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±8分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,20 +7360,377 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>74.8</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
         <is>
           <t>4/14</t>
         </is>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,22 +3203,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,17 +3322,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,22 +3441,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,22 +3679,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,17 +4274,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,17 +4631,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,17 +5583,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,17 +5821,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6307,12 +6307,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6362,12 +6362,12 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6469,24 +6469,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -6600,10 +6600,14 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:22采样，终点ETA 39分钟</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -6611,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6635,12 +6639,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6665,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6702,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -6715,12 +6719,12 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>14:22采样：该车到重点站唐陆公路龙东大道 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6730,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6754,12 +6758,12 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6779,12 +6783,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6817,29 +6821,29 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>14:22采样：该车到重点站博兴路东陆路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±10分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6849,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6873,12 +6877,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6898,12 +6902,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6936,12 +6940,12 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -6953,12 +6957,12 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>14:22采样：该车到重点站唐陆公路龙东大道 ETA 32分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6968,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6992,12 +6996,12 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7007,17 +7011,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7055,24 +7059,24 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -7087,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7111,12 +7115,12 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7136,12 +7140,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7179,19 +7183,19 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：15:22采样，终点ETA 34分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
@@ -7202,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7226,37 +7230,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7294,19 +7298,19 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>61分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±5分钟</t>
+          <t>同车下一次反向发车16:20，减去该车自身同类时段历史终点停站中位数19分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -7321,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7350,7 +7354,7 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7360,22 +7364,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7413,24 +7417,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±8分钟</t>
+          <t>15:22采样：该车到重点站东陆路金海路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7440,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7469,7 +7473,7 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7489,12 +7493,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7532,24 +7536,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+          <t>15:22采样：该车到重点站新德西路德翔路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7559,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7588,7 +7592,7 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7608,12 +7612,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7656,19 +7660,19 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±9分钟</t>
+          <t>15:22采样：该车到重点站长岛路台儿庄路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7678,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7707,32 +7711,742 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>69分钟</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y61" s="2" t="inlineStr">
+      <c r="Y62" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>4/14</t>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3208,17 +3208,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,22 +3560,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,22 +3798,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,22 +4155,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,22 +4274,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,22 +4631,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,22 +5345,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,22 +6059,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,22 +6178,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,22 +6297,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,22 +6416,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,22 +6892,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7059,31 +7059,27 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：15:42采样，终点ETA 9分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7091,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7115,12 +7111,12 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7130,22 +7126,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7178,27 +7174,31 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:22采样，终点ETA 34分钟</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7293,24 +7293,24 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>61分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车16:20，减去该车自身同类时段历史终点停站中位数19分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7369,17 +7369,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7412,12 +7412,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>15:22采样：该车到重点站东陆路金海路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -7548,12 +7548,12 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>15:22采样：该车到重点站新德西路德翔路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7602,22 +7602,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7650,29 +7650,29 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>15:22采样：该车到重点站长岛路台儿庄路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -7769,29 +7769,29 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数69分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7840,22 +7840,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7893,26 +7893,22 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:22采样，终点ETA 38分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7920,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7944,12 +7940,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7969,7 +7965,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8012,24 +8008,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±14分钟</t>
+          <t>16:22采样：该车到重点站唐陆公路龙东大道 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8039,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,12 +8059,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8078,22 +8074,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8131,24 +8127,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±12分钟</t>
+          <t>16:22采样：该车到重点站德川路华夏东路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8158,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8187,7 +8183,7 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8207,7 +8203,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8250,19 +8246,19 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±13分钟</t>
+          <t>16:22采样：该车到重点站唐陆公路川桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -8277,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8306,7 +8302,7 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8326,12 +8322,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8339,24 +8335,24 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沪A12050A</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8369,30 +8365,34 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>16:22采样：该车到重点站新川路华东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8406,47 +8406,880 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr">
         <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
           <t>16:20</t>
         </is>
       </c>
-      <c r="V67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>16:22采样：该车到重点站唐陆公路川桥路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W67" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="X67" s="2" t="inlineStr">
-        <is>
-          <t>证据不足</t>
-        </is>
-      </c>
-      <c r="Y67" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z67" s="2" t="inlineStr">
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
-        <is>
-          <t>2/14</t>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,22 +2850,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,22 +3322,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,22 +3441,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,22 +3560,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,22 +3679,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,22 +3798,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,22 +4393,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,22 +4512,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,22 +4869,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,17 +5350,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,22 +5702,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,22 +6059,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,22 +6178,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,22 +6535,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,22 +6654,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6773,22 +6773,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,22 +6892,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7011,22 +7011,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7245,22 +7245,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7483,22 +7483,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7607,17 +7607,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7655,24 +7655,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7721,22 +7721,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7888,27 +7888,31 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:22采样，终点ETA 38分钟</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7916,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7940,12 +7944,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7955,22 +7959,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8003,29 +8007,29 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>16:22采样：该车到重点站唐陆公路龙东大道 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±10分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8035,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8059,12 +8063,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8084,12 +8088,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8122,29 +8126,29 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>16:22采样：该车到重点站德川路华夏东路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±13分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8154,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,12 +8182,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8193,22 +8197,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8241,29 +8245,29 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>16:22采样：该车到重点站唐陆公路川桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±13分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8273,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,12 +8301,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8312,22 +8316,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8360,29 +8364,29 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>16:22采样：该车到重点站新川路华东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8392,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8416,12 +8420,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8431,22 +8435,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8479,29 +8483,29 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>16:22采样：该车到重点站唐陆公路川桥路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±13分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8511,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8535,12 +8539,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8560,12 +8564,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8603,26 +8607,22 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 33分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8669,22 +8669,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8722,24 +8722,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±9分钟</t>
+          <t>17:21采样：该车到重点站唐陆公路锦绣东路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8841,26 +8841,22 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 48分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8868,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8892,17 +8888,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8912,17 +8908,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8960,19 +8956,19 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>17:21采样：该车到重点站新德西路德翔路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -8987,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9016,7 +9012,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9036,12 +9032,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9049,24 +9045,24 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9079,34 +9075,34 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±8分钟</t>
+          <t>17:21采样：该车到重点站新德西路德翔路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9135,7 +9131,7 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9155,12 +9151,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9164,7 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -9178,7 +9174,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -9198,34 +9194,34 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±15分钟</t>
+          <t>17:21采样：该车到重点站东陆路金海路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9239,47 +9235,999 @@
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="V74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr">
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>17:21采样：该车到重点站长岛路台儿庄路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X74" s="2" t="inlineStr">
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y74" s="2" t="inlineStr">
+      <c r="Y77" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z74" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>79.7</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
         <is>
           <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,22 +3441,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,22 +4155,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,22 +4393,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,22 +4631,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,22 +5345,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,22 +6297,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,22 +6416,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,22 +6535,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6773,22 +6773,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7126,22 +7126,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7483,22 +7483,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7602,22 +7602,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7721,22 +7721,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7840,22 +7840,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8088,12 +8088,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8197,22 +8197,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8488,24 +8488,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8602,27 +8602,31 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 33分钟</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8630,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8654,12 +8658,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8679,12 +8683,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8717,29 +8721,29 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站唐陆公路锦绣东路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8749,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8773,12 +8777,12 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8788,22 +8792,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8836,27 +8840,31 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 48分钟</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8864,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8888,37 +8896,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8956,26 +8964,22 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站新德西路德翔路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:02采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -8983,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9012,7 +9016,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9022,22 +9026,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9075,26 +9079,22 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站新德西路德翔路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 21分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9141,22 +9141,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9189,24 +9189,24 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站东陆路金海路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9260,22 +9260,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9313,24 +9313,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>18:02采样：该车到重点站新德西路德翔路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -9427,29 +9427,29 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站长岛路台儿庄路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±14分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9551,24 +9551,24 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±9分钟</t>
+          <t>同车下一次反向发车19:30，减去该车自身同类时段历史终点停站中位数26分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9617,22 +9617,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9670,26 +9670,22 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 37分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9697,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9721,12 +9717,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9736,22 +9732,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9789,24 +9785,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±8分钟</t>
+          <t>18:21采样：该车到重点站唐陆公路川桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9816,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9845,7 +9841,7 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9865,7 +9861,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9908,24 +9904,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±9分钟</t>
+          <t>18:21采样：该车到重点站唐陆公路龙东大道 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9935,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9964,7 +9960,7 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9984,12 +9980,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10003,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -10032,19 +10028,19 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数96分钟估算，约±8分钟</t>
+          <t>18:21采样：该车到重点站唐陆公路川桥路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10054,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10068,7 +10064,7 @@
       <c r="T81" s="2" t="inlineStr"/>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
@@ -10083,7 +10079,7 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10103,12 +10099,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10116,24 +10112,24 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
-        </is>
-      </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10146,24 +10142,24 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±9分钟</t>
+          <t>18:21采样：该车到重点站金杨路金桥路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10173,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10202,32 +10198,865 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>81.1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>18:21采样：该车到重点站新川路华东路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>19:49</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y82" s="2" t="inlineStr">
+      <c r="Y84" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z82" s="2" t="inlineStr">
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
+      <c r="AA85" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
-        <is>
-          <t>77.1</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr">
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
         <is>
           <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数93分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>83.1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>76.3</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>20:38</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>78.6</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,22 +3322,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,22 +3679,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,22 +3798,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,22 +4869,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,22 +5345,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,22 +6178,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7011,22 +7011,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7245,22 +7245,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7602,22 +7602,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7959,22 +7959,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8088,12 +8088,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8316,22 +8316,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8435,22 +8435,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8911,22 +8911,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9074,27 +9074,31 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 21分钟</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9102,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9126,12 +9130,12 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9151,12 +9155,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9270,12 +9274,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9432,12 +9436,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -9459,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9508,12 +9512,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9546,24 +9550,24 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车19:30，减去该车自身同类时段历史终点停站中位数26分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -9578,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9602,12 +9606,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9627,12 +9631,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9665,27 +9669,31 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 37分钟</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9693,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9717,12 +9725,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9742,7 +9750,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9780,29 +9788,29 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站唐陆公路川桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9812,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9836,12 +9844,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9851,22 +9859,22 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9899,29 +9907,29 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站唐陆公路龙东大道 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9931,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9955,12 +9963,12 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9970,22 +9978,22 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10018,29 +10026,29 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站唐陆公路川桥路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10050,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10074,12 +10082,12 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10099,12 +10107,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10142,24 +10150,24 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站金杨路金桥路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
+          <t>18:41采样：该车到重点站东陆路金海路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10169,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10218,7 +10226,7 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10256,29 +10264,29 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站新川路华东路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10288,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10312,12 +10320,12 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10327,22 +10335,22 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -10380,26 +10388,22 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 30分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -10407,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10431,12 +10435,12 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10456,12 +10460,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10499,19 +10503,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±8分钟</t>
+          <t>同车下一次反向发车20:10，减去该车自身同类时段历史终点停站中位数22分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -10526,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10555,7 +10559,7 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10565,22 +10569,22 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10618,19 +10622,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数93分钟估算，约±12分钟</t>
+          <t>19:21采样：该车到重点站唐陆公路春雅路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10645,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10674,7 +10678,7 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10694,12 +10698,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10737,24 +10741,24 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±8分钟</t>
+          <t>19:21采样：该车到重点站新德西路德翔路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10764,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10793,7 +10797,7 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10813,12 +10817,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10856,24 +10860,24 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±6分钟</t>
+          <t>19:21采样：该车到重点站东陆路金海路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10883,7 +10887,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10912,7 +10916,7 @@
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10932,7 +10936,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10945,22 +10949,22 @@
       <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10987,22 +10991,22 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11051,12 +11055,488 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>81.6</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>76.1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>78.6</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -451,9 +451,9 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,14 +2136,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>78.6</t>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,22 +3441,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,14 +3798,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>78.6</t>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,22 +4631,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,14 +5226,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>78.6</t>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,14 +6178,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>78.6</t>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7840,22 +7840,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8197,22 +8197,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8435,14 +8435,14 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
           <t>78.6</t>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8921,12 +8921,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9264,22 +9264,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9621,22 +9621,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9859,14 +9859,14 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
           <t>78.6</t>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10269,24 +10269,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10345,12 +10345,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10388,19 +10388,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 30分钟</t>
+          <t>SHMAAS末次终点ETA推算：19:41采样，终点ETA 9分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10498,29 +10498,29 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车20:10，减去该车自身同类时段历史终点停站中位数22分钟，约±8分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10579,12 +10579,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -10617,29 +10617,29 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站唐陆公路春雅路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±12分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10673,12 +10673,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10736,29 +10736,29 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站新德西路德翔路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10807,22 +10807,22 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -10855,24 +10855,24 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站东陆路金海路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10936,12 +10936,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10974,29 +10974,29 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11093,29 +11093,29 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11164,22 +11164,22 @@
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11217,19 +11217,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±13分钟</t>
+          <t>20:21采样：该车到重点站唐陆公路龙东大道 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
@@ -11293,12 +11293,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -11336,26 +11336,22 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 56分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11363,7 +11359,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11387,29 +11383,29 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA92" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
           <t>78.6</t>
@@ -11417,7 +11413,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -11467,7 +11463,7 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±11分钟</t>
+          <t>20:21采样：该车到重点站博兴路东陆路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -11482,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11511,32 +11507,389 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y93" s="2" t="inlineStr">
+      <c r="Y94" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z93" s="2" t="inlineStr">
+      <c r="Z94" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AA93" s="2" t="inlineStr">
+      <c r="AA94" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AB93" s="2" t="inlineStr">
-        <is>
-          <t>77.1</t>
-        </is>
-      </c>
-      <c r="AC93" s="2" t="inlineStr">
-        <is>
-          <t>3/14</t>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>80.1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>78.6</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -436,12 +436,12 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -451,9 +451,9 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2855,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3012,29 +3012,29 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:52采样，终点ETA 11分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
@@ -3069,17 +3069,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3446,17 +3446,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3803,17 +3803,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3922,17 +3922,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4160,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4517,17 +4517,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4755,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5112,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,17 +5350,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5469,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5707,17 +5707,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5945,17 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6183,17 +6183,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6302,17 +6302,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6421,17 +6421,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -6659,17 +6659,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6778,17 +6778,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7054,29 +7054,29 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:42采样，终点ETA 9分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
@@ -7111,17 +7111,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7131,17 +7131,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7250,17 +7250,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7607,17 +7607,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7726,17 +7726,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7845,17 +7845,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8321,17 +8321,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8440,17 +8440,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8797,17 +8797,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8916,17 +8916,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8954,29 +8954,29 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:02采样，终点ETA 19分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr"/>
@@ -9011,17 +9011,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9031,17 +9031,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9269,17 +9269,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9307,36 +9307,32 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>18:02采样：该车到重点站新德西路德翔路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -9368,17 +9364,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9388,17 +9384,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9626,17 +9622,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9745,17 +9741,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9864,17 +9860,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9993,7 +9989,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10108,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10140,36 +10136,32 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>18:41采样：该车到重点站东陆路金海路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10201,17 +10193,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10221,17 +10213,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10340,17 +10332,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10378,29 +10370,29 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:41采样，终点ETA 9分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
@@ -10435,17 +10427,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10455,17 +10447,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10574,17 +10566,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10812,17 +10804,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10931,17 +10923,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -11006,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11060,7 +11052,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -11098,24 +11090,24 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11125,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11169,17 +11161,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11207,36 +11199,32 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站唐陆公路龙东大道 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±13分钟</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11244,7 +11232,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11268,17 +11256,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11288,17 +11276,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -11326,29 +11314,29 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 56分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr"/>
@@ -11359,7 +11347,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11388,7 +11376,7 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11403,17 +11391,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11441,36 +11429,32 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站博兴路东陆路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11478,7 +11462,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11502,17 +11486,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11522,17 +11506,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -11560,36 +11544,32 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>21:41</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -11597,7 +11577,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11621,17 +11601,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11641,17 +11621,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11679,36 +11659,32 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11716,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11740,17 +11716,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11760,17 +11736,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11788,7 +11764,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -11798,36 +11774,32 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11835,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11854,22 +11826,22 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+          <t>计划发车</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11879,17 +11851,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-23-182路.xlsx
+++ b/data/export/2026-09-23-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5112,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7250,17 +7250,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8321,17 +8321,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9269,12 +9269,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10332,17 +10332,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10971,24 +10971,24 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11199,32 +11199,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11232,7 +11236,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11256,17 +11260,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11276,17 +11280,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11347,7 +11351,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11429,32 +11433,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11462,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11486,17 +11494,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11506,12 +11514,12 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11544,32 +11552,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -11577,7 +11589,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11601,17 +11613,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11621,12 +11633,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11692,7 +11704,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11807,7 +11819,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
